--- a/outputs/orientacoes/CS_EQUIPAMENTOS_ORIENTACOES.xlsx
+++ b/outputs/orientacoes/CS_EQUIPAMENTOS_ORIENTACOES.xlsx
@@ -15829,8 +15829,7 @@
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
-          <t>verde: 64—112°C (147.2—233.6 F)
-●Faixa de área vermelha: 113—116°C</t>
+          <t>verde: 64—112°C (147.2—233.6 F) ●Faixa de área vermelha: 113—116°C</t>
         </is>
       </c>
       <c r="O228" t="n">
@@ -15902,8 +15901,7 @@
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
-          <t>verde: -18°C—92°C (-0.4—197.6°F)
-●Faixa de área vermelha: 93°C—102°C</t>
+          <t>verde: -18°C—92°C (-0.4—197.6°F) ●Faixa de área vermelha: 93°C—102°C</t>
         </is>
       </c>
       <c r="O229" t="n">
@@ -15975,9 +15973,7 @@
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
-          <t>verde: 35—100%
-●Faixa de área amarela: 101—110%
-●Faixa de área vermelha: 111—114%</t>
+          <t>verde: 35—100% ●Faixa de área amarela: 101—110% ●Faixa de área vermelha: 111—114%</t>
         </is>
       </c>
       <c r="O230" t="n">
@@ -16049,9 +16045,7 @@
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr">
         <is>
-          <t>verde: 35—100%
-●Faixa de área amarela: 101—110%
-●Faixa de área vermelha: 111—114%</t>
+          <t>verde: 35—100% ●Faixa de área amarela: 101—110% ●Faixa de área vermelha: 111—114%</t>
         </is>
       </c>
       <c r="O231" t="n">
@@ -16123,10 +16117,7 @@
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr">
         <is>
-          <t>nível atingir 10% de
-Visão Geral da Cabine e dos Controles da Colhedora de Cana-de-Açúcar
-25-6
-combustível restante</t>
+          <t>nível atingir 10% de Visão Geral da Cabine e dos Controles da Colhedora de Cana-de-Açúcar 25-6 combustível restante</t>
         </is>
       </c>
       <c r="O232" t="n">
@@ -16194,10 +16185,7 @@
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr">
         <is>
-          <t>nível atinge 10%, o indicador de nível
-pisca, o alerta soa e aparece uma mensagem que
-indica que o nível de fluido está baixo.
-●Quando o nível atinge 0%</t>
+          <t>nível atinge 10%, o indicador de nível pisca, o alerta soa e aparece uma mensagem que indica que o nível de fluido está baixo. ●Quando o nível atinge 0%</t>
         </is>
       </c>
       <c r="O233" t="n">
@@ -16265,10 +16253,7 @@
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr">
         <is>
-          <t>nível atinge 10%, o indicador de nível
-pisca, o alerta soa e aparece uma mensagem que
-indica que o nível de fluido está baixo.
-●Quando o nível atinge 0%</t>
+          <t>nível atinge 10%, o indicador de nível pisca, o alerta soa e aparece uma mensagem que indica que o nível de fluido está baixo. ●Quando o nível atinge 0%</t>
         </is>
       </c>
       <c r="O234" t="n">
@@ -16336,8 +16321,7 @@
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr">
         <is>
-          <t>0—25.000 kPa
-(0—250 bar)</t>
+          <t>0—25.000 kPa (0—250 bar)</t>
         </is>
       </c>
       <c r="O235" t="n">
@@ -16545,8 +16529,7 @@
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr">
         <is>
-          <t>80 a 84 °C (175 a 182 °F)
-94 °C</t>
+          <t>80 a 84 °C (175 a 182 °F) 94 °C</t>
         </is>
       </c>
       <c r="O238" t="n">
@@ -16622,24 +16605,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>●Uso de um filtro de óleo aprovado pela John
-Deere.
-Intervalos de Serviço do Filtro e do Óleo do Motor
-Enxofre no
-Combustível
-Menos de 5000 mg/kg (5000 ppm)
-Óleos Plus-50
-500 horas de operação
-Outros óleos
-250 horas
-Enxofre no
-Combustível
-5.000–10.000 mg/kg (5.000–10.000 ppm)
-Óleos Plus-50
-250 horas
-Outros óleos
-125 horas de operação
-A análise do óleo pode estender o intervalo de serviço de “outro</t>
+          <t>●Uso de um filtro de óleo aprovado pela John Deere. Intervalos de Serviço do Filtro e do Óleo do Motor Enxofre no Combustível Menos de 5000 mg/kg (5000 ppm) Óleos Plus-50 500 horas de operação Outros óleos 250 horas Enxofre no Combustível 5.000–10.000 mg/kg (5.000–10.000 ppm) Óleos Plus-50 250 horas Outros óleos 125 horas de operação A análise do óleo pode estender o intervalo de serviço de “outro</t>
         </is>
       </c>
       <c r="O239" t="n">
@@ -16707,8 +16673,7 @@
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr">
         <is>
-          <t>temperatura for inferior a 0 °C (32 °F), o
-combustível para inverno</t>
+          <t>temperatura for inferior a 0 °C (32 °F), o combustível para inverno</t>
         </is>
       </c>
       <c r="O240" t="n">
@@ -17803,8 +17768,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>verde: 64—112°C (147.2—233.6 F)
-●Faixa de área vermelha: 113—116°C</t>
+          <t>verde: 64—112°C (147.2—233.6 F) ●Faixa de área vermelha: 113—116°C</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -17876,8 +17840,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>verde: -18°C—92°C (-0.4—197.6°F)
-●Faixa de área vermelha: 93°C—102°C</t>
+          <t>verde: -18°C—92°C (-0.4—197.6°F) ●Faixa de área vermelha: 93°C—102°C</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -17949,9 +17912,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>verde: 35—100%
-●Faixa de área amarela: 101—110%
-●Faixa de área vermelha: 111—114%</t>
+          <t>verde: 35—100% ●Faixa de área amarela: 101—110% ●Faixa de área vermelha: 111—114%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -18023,9 +17984,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>verde: 35—100%
-●Faixa de área amarela: 101—110%
-●Faixa de área vermelha: 111—114%</t>
+          <t>verde: 35—100% ●Faixa de área amarela: 101—110% ●Faixa de área vermelha: 111—114%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -18097,10 +18056,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>nível atingir 10% de
-Visão Geral da Cabine e dos Controles da Colhedora de Cana-de-Açúcar
-25-6
-combustível restante</t>
+          <t>nível atingir 10% de Visão Geral da Cabine e dos Controles da Colhedora de Cana-de-Açúcar 25-6 combustível restante</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -18168,10 +18124,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>nível atinge 10%, o indicador de nível
-pisca, o alerta soa e aparece uma mensagem que
-indica que o nível de fluido está baixo.
-●Quando o nível atinge 0%</t>
+          <t>nível atinge 10%, o indicador de nível pisca, o alerta soa e aparece uma mensagem que indica que o nível de fluido está baixo. ●Quando o nível atinge 0%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -18239,10 +18192,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>nível atinge 10%, o indicador de nível
-pisca, o alerta soa e aparece uma mensagem que
-indica que o nível de fluido está baixo.
-●Quando o nível atinge 0%</t>
+          <t>nível atinge 10%, o indicador de nível pisca, o alerta soa e aparece uma mensagem que indica que o nível de fluido está baixo. ●Quando o nível atinge 0%</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -18310,8 +18260,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0—25.000 kPa
-(0—250 bar)</t>
+          <t>0—25.000 kPa (0—250 bar)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -18519,8 +18468,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>80 a 84 °C (175 a 182 °F)
-94 °C</t>
+          <t>80 a 84 °C (175 a 182 °F) 94 °C</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -18596,24 +18544,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>●Uso de um filtro de óleo aprovado pela John
-Deere.
-Intervalos de Serviço do Filtro e do Óleo do Motor
-Enxofre no
-Combustível
-Menos de 5000 mg/kg (5000 ppm)
-Óleos Plus-50
-500 horas de operação
-Outros óleos
-250 horas
-Enxofre no
-Combustível
-5.000–10.000 mg/kg (5.000–10.000 ppm)
-Óleos Plus-50
-250 horas
-Outros óleos
-125 horas de operação
-A análise do óleo pode estender o intervalo de serviço de “outro</t>
+          <t>●Uso de um filtro de óleo aprovado pela John Deere. Intervalos de Serviço do Filtro e do Óleo do Motor Enxofre no Combustível Menos de 5000 mg/kg (5000 ppm) Óleos Plus-50 500 horas de operação Outros óleos 250 horas Enxofre no Combustível 5.000–10.000 mg/kg (5.000–10.000 ppm) Óleos Plus-50 250 horas Outros óleos 125 horas de operação A análise do óleo pode estender o intervalo de serviço de “outro</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -18681,8 +18612,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>temperatura for inferior a 0 °C (32 °F), o
-combustível para inverno</t>
+          <t>temperatura for inferior a 0 °C (32 °F), o combustível para inverno</t>
         </is>
       </c>
       <c r="O14" t="n">
